--- a/building_inspector_forms/029_flooring_inspection_checklist--building_inspector_forms.xlsx
+++ b/building_inspector_forms/029_flooring_inspection_checklist--building_inspector_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>hard_wood</t>
+          <t>hard wood</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>wood_engineered</t>
+          <t>wood engineered</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cork_par</t>
+          <t>cork par</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>cork_par</t>
+          <t>cork_par_with_wood</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cork_par</t>
+          <t>cork par with wood</t>
         </is>
       </c>
     </row>
@@ -1284,29 +1284,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>cork_par_with_wood</t>
+          <t>cork_par_with_plywood</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>cork_par_with_wood</t>
+          <t>cork par with plywood</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>floor_type_choices</t>
+          <t>flooring_condition_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>cork_par_with_plywood</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>cork_par_with_plywood</t>
+          <t>excellent</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>good</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>fair</t>
         </is>
       </c>
     </row>
@@ -1352,29 +1352,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>poor</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>flooring_condition_choices</t>
+          <t>damage_present_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1386,19 +1386,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>damage_present_choices</t>
+          <t>inspection_completed_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1420,29 +1420,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>inspection_completed_choices</t>
+          <t>final_inspection_result_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>pass</t>
         </is>
       </c>
     </row>
@@ -1454,27 +1454,10 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>final_inspection_result_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>fail</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
         <is>
           <t>fail</t>
         </is>
